--- a/AAII_Financials/Yearly/KLPPY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KLPPY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>KLPPY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -655,135 +655,147 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2046700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1755300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1701100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1673200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1602600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1640500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1834000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1897300</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>448900</v>
+      </c>
+      <c r="E9" s="3">
         <v>382900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>399000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>420200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>421800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>560400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>439800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>471900</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1597900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1372400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1302100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1253000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1180800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1080100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1394200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1425300</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -795,8 +807,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -821,9 +834,12 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -848,63 +864,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-818200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-556400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>543300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>422500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>563700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1923200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>551200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-319800</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E15" s="3">
         <v>17600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>17700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>20600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>24500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>22900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14900</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -913,62 +938,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>739300</v>
+      </c>
+      <c r="E17" s="3">
         <v>612700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>609600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>614000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>609600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>753500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>650700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>705200</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1307400</v>
+      </c>
+      <c r="E18" s="3">
         <v>1142600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1091500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1059200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>993100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>887000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1183400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1192100</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -980,143 +1012,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>69300</v>
+        <v>50800</v>
       </c>
       <c r="E20" s="3">
+        <v>76700</v>
+      </c>
+      <c r="F20" s="3">
         <v>126300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>20400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>56900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>60500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>61800</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1090900</v>
+        <v>1276200</v>
       </c>
       <c r="E21" s="3">
+        <v>1083400</v>
+      </c>
+      <c r="F21" s="3">
         <v>984700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1073000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>993300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>854600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1145800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1145200</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>326900</v>
+      </c>
+      <c r="E22" s="3">
         <v>263800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>229400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>131100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>141200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>209200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>210000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>206300</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1899400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1485900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>304100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>535000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>294600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1226300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>444500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1303100</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>186900</v>
+      </c>
+      <c r="E24" s="3">
         <v>192600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>111400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>75700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-356000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-87200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>27200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>125000</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1141,63 +1189,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1712500</v>
+      </c>
+      <c r="E26" s="3">
         <v>1293300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>192700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>459300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>650500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1139100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>417300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1178000</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1525700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1136300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>213000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>443700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>619500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-961100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>364600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>960400</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1222,9 +1279,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1249,9 +1309,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1276,9 +1339,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1303,63 +1369,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-69300</v>
+        <v>-50800</v>
       </c>
       <c r="E32" s="3">
+        <v>-76700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-126300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-20400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-56900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-60500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-61800</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1525700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1136200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>213000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>443700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>619500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-961100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>364600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>960400</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1384,68 +1459,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1525700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1136200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>213000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>443700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>619500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-961100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>364600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>960400</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1457,8 +1541,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1470,35 +1555,39 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>976800</v>
+      </c>
+      <c r="E41" s="3">
         <v>414900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>396500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>301000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>727900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>565300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>543700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>348600</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1523,36 +1612,42 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>254600</v>
+        <v>257000</v>
       </c>
       <c r="E43" s="3">
+        <v>233800</v>
+      </c>
+      <c r="F43" s="3">
         <v>286400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>274300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>319900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>366700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>304600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>327900</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1577,144 +1672,162 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>272000</v>
+        <v>301900</v>
       </c>
       <c r="E45" s="3">
+        <v>292800</v>
+      </c>
+      <c r="F45" s="3">
         <v>318700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>293800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>272600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>302800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>391900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>298500</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1535600</v>
+      </c>
+      <c r="E46" s="3">
         <v>941500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1001500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>874000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1336700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1254700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1240200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>975000</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1096600</v>
+        <v>1279700</v>
       </c>
       <c r="E47" s="3">
+        <v>1095100</v>
+      </c>
+      <c r="F47" s="3">
         <v>1075500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1062700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1113800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1210900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1232300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1203800</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22425700</v>
+      </c>
+      <c r="E48" s="3">
         <v>18878000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19243900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19112300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21409100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24363300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24101300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25042700</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>589300</v>
+      </c>
+      <c r="E49" s="3">
         <v>507300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>541800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>528900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>571400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>741800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>708600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>739100</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1739,9 +1852,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1766,36 +1882,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>271200</v>
+        <v>303000</v>
       </c>
       <c r="E52" s="3">
+        <v>272700</v>
+      </c>
+      <c r="F52" s="3">
         <v>318900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>371900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>328600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>403800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>342300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>375800</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1820,36 +1942,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26145600</v>
+      </c>
+      <c r="E54" s="3">
         <v>21713300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22209400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21963400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>24773000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27993500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27649000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>28360100</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1861,8 +1989,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1874,170 +2003,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E57" s="3">
         <v>155600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>178600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>177100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>249200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>246000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>139400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>166800</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1973300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1425900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1771600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2127500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2185900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2942500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2674800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2626900</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>468400</v>
+      </c>
+      <c r="E59" s="3">
         <v>430100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>421800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>481400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>534900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>518200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>580300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>533300</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2725600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2158700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2556400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2923100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3138100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3859400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3527300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3463700</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8023400</v>
+      </c>
+      <c r="E61" s="3">
         <v>6955100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7035400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6395600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8152500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9298000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8371800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8056200</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>322100</v>
+      </c>
+      <c r="E62" s="3">
         <v>273300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>306400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>311400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>192300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>212800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>195200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>220600</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2062,9 +2210,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2089,9 +2240,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2116,36 +2270,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12685900</v>
+      </c>
+      <c r="E66" s="3">
         <v>10688200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11134300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10785700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12725500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15229700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13892800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13598000</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2157,8 +2317,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2183,9 +2344,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2210,9 +2374,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2237,9 +2404,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2264,36 +2434,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1136200</v>
+        <v>4849100</v>
       </c>
       <c r="E72" s="3">
+        <v>4614700</v>
+      </c>
+      <c r="F72" s="3">
         <v>213000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>490800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>669500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-907300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>414100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1010800</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2318,9 +2494,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2345,9 +2524,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2372,36 +2554,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10947500</v>
+      </c>
+      <c r="E76" s="3">
         <v>8901200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8861200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8939000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9558400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10008900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10969000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11858800</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2426,68 +2614,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1525700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1136200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>213000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>443700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>619500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-961100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>364600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>960400</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2499,35 +2696,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E83" s="3">
         <v>17600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>19600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>30700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>166200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>22900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14900</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2552,9 +2753,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2579,9 +2783,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2606,9 +2813,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2633,9 +2843,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2660,36 +2873,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1203600</v>
+      </c>
+      <c r="E89" s="3">
         <v>999100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1032200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>973000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>984600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>972500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1169800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1168100</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2701,35 +2920,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6800</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2754,9 +2977,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2781,36 +3007,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-218000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-285300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-52900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>403000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>765400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-76100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>281900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>159500</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2822,35 +3054,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>621300</v>
+      </c>
+      <c r="E96" s="3">
         <v>502300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>285700</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>768300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>695200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>674800</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2875,9 +3111,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2902,9 +3141,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2929,88 +3171,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-471400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-669100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-892900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1738700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1549300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-898600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1027400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1724500</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4200</v>
       </c>
-      <c r="I101" s="3" t="s">
+      <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9200</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>505700</v>
+      </c>
+      <c r="E102" s="3">
         <v>43700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>85100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-366600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>195400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>424300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-406100</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
